--- a/frontend/public/templates/Location_Master_Import_Template.xlsx
+++ b/frontend/public/templates/Location_Master_Import_Template.xlsx
@@ -647,6 +647,11 @@
           <t>C</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>01</t>
@@ -697,6 +702,11 @@
       <c r="G5" t="inlineStr">
         <is>
           <t>D</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -731,7 +741,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -739,7 +748,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -750,7 +758,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2. Which of Rack/Level/Bin, Block, or Stack applies depends on Storage Type: SPR/Drive-in use Rack + Level (Bin optional, defaults to "1"); Ground/Floor uses Block (+ Depth/Width required, Height optional); Stillage uses Stack (+ Height required, Depth/Width optional). Leave the columns that don't apply to your Storage Type blank.</t>
+          <t>2. Which of Rack/Level/Bin, Block, or Stack applies depends on Storage Type: SPR/Drive-in use Rack + Level (Bin optional, defaults to "1"); Ground/Floor uses Block + Rack (the column number) + Depth/Width required; Stillage uses Stack + Rack (the column number, 2026-09-13) + Height required, Depth/Width optional (default 1). Leave the columns that don't apply to your Storage Type blank.</t>
         </is>
       </c>
     </row>
@@ -947,12 +955,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Required for SPR/Drive-in only</t>
+          <t>Rack: required for SPR/Drive-in AND (2026-09-13) Ground/Floor/Stillage (column number). Level: SPR/Drive-in only.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rack identifies the bay position along the aisle; Level is the shelf/racking level.</t>
+          <t>Rack identifies the bay position along the aisle for SPR/Drive-in, OR the COLUMN number (1..Width) within the bin for Ground/Floor and Stillage. Level is the shelf/racking level (SPR/Drive-in only).</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1011,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Identifies the stillage stack/column.</t>
+          <t>Identifies the Stillage bin as a whole (e.g. "01") — which COLUMN within it uses the Rack field above (rule 9), same as Ground/Floor's own Block+Rack split.</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1028,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Whole number. Rack: which position in a multi-deep lane (1 = front). Ground/Floor: pallets deep. Stillage: stillage columns deep (defaults to 1).</t>
+          <t>Whole number. Rack: which position in a multi-deep lane (1 = front). Ground/Floor: this pallet’s position within its column (1 = front). Stillage: this position’s place within its column (1 = front, defaults to 1).</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1045,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Whole number. Ground/Floor: stacks wide. Stillage: stillage columns wide (defaults to 1).</t>
+          <t>Whole number. Ground/Floor: how many columns the whole bin has. Stillage: how many columns the whole stack has (defaults to 1).</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1062,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Whole number. Ground/Floor: layers stacked (defaults to 1). Stillage: stillages stacked.</t>
+          <t>Whole number. Ground/Floor: layers stacked (defaults to 1, no vertical stacking on the ground). Stillage: stillages stacked vertically at this exact position (required).</t>
         </is>
       </c>
     </row>
